--- a/output/pdf_financials_xlsx/RUS.xlsx
+++ b/output/pdf_financials_xlsx/RUS.xlsx
@@ -4869,70 +4869,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>26.2</v>
       </c>
     </row>
     <row r="77">
@@ -5393,43 +5367,43 @@
         <v>3.9</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>39.9</v>
+        <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>18</v>
+        <v>633.6</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>30.4</v>
+        <v>602.6</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>21.4</v>
+        <v>666.9</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>26.2</v>
+        <v>771.2</v>
       </c>
     </row>
     <row r="86">
@@ -5498,25 +5472,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N86" s="3" t="n">
+        <v>929.6</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>899.8</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>666.9</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>1069.5</v>
       </c>
     </row>
     <row r="87">
@@ -10244,7 +10210,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12730,7 +12696,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14102,7 +14068,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">

--- a/output/pdf_financials_xlsx/RUS.xlsx
+++ b/output/pdf_financials_xlsx/RUS.xlsx
@@ -1005,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>-0.0001504</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>83.2</v>
+        <v>84.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>169.4</v>
+        <v>171.4</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>138.1</v>
+        <v>139.8</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2164,13 +2164,13 @@
         <v>-0.0001247</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>108.5</v>
+        <v>110.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>192.9</v>
+        <v>194.9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>163.6</v>
+        <v>165.3</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2235,13 +2235,13 @@
         <v>-6.324170808398417</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.981634527089073</v>
+        <v>5.055096418732782</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>7.162217354175175</v>
+        <v>7.236475698956671</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.453151561614613</v>
+        <v>5.509816339455352</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -40058,7 +40058,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -43574,7 +43574,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -44510,7 +44510,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -45828,7 +45828,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -45922,7 +45922,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -46480,7 +46480,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -47978,7 +47978,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">

--- a/output/pdf_financials_xlsx/RUS.xlsx
+++ b/output/pdf_financials_xlsx/RUS.xlsx
@@ -2788,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -2843,13 +2843,13 @@
         <v>0.0003014</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>382.4</v>
+        <v>384.7</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>456.2</v>
+        <v>462.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>456.2</v>
+        <v>464.7</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>569.3</v>
@@ -3228,13 +3228,13 @@
         <v>1150.7988308</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.8</v>
+        <v>8.5</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.2</v>
+        <v>3.7</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>14.4</v>
@@ -3903,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>120.2</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>145.8</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>131.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-8.64e-05</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-27.9</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-81.5</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-133.6</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-87.3</v>
       </c>
     </row>
     <row r="122">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -25792,7 +25792,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -35076,7 +35080,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
         <v>-1.8e-06</v>
       </c>
@@ -36308,7 +36316,11 @@
           <t>Purchase of common shares (Note 14)</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E305" s="5" t="n">
         <v>-8.64e-05</v>
       </c>
@@ -50678,7 +50690,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E462" s="5" t="n">
         <v>0.0002285</v>
       </c>
